--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,59 +656,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -736,8 +740,11 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -765,8 +772,11 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,8 +804,11 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,37 +820,41 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>800</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
-        <v>700</v>
-      </c>
       <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,8 +882,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -894,8 +914,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -923,8 +946,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,37 +959,41 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
-        <v>2000</v>
-      </c>
       <c r="G17" s="3">
+        <v>700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>500</v>
+      </c>
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -971,28 +1001,31 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,8 +1037,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1016,16 +1050,16 @@
         <v>-200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1033,8 +1067,11 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1062,16 +1099,19 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1079,8 +1119,8 @@
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1091,37 +1131,43 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1149,8 +1195,11 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,66 +1227,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1355,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,8 +1419,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1364,16 +1434,16 @@
         <v>200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1381,37 +1451,43 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,71 +1515,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,20 +1614,21 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,8 +1644,11 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1586,8 +1676,11 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1615,8 +1708,11 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1644,20 +1740,23 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1673,20 +1772,23 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2200</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1702,8 +1804,11 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1731,16 +1836,19 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
         <v>0</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+      <c r="E48" s="3">
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -1760,8 +1868,11 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1789,8 +1900,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,20 +1964,23 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,8 +1996,11 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,20 +2028,23 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2400</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,8 +2060,11 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,20 +2090,21 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,8 +2120,11 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2018,8 +2152,11 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2027,10 +2164,10 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
@@ -2047,20 +2184,23 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>400</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2076,20 +2216,23 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -2105,20 +2248,23 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>5000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4800</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2134,8 +2280,11 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,20 +2376,23 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5300</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2250,8 +2408,11 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2350,8 +2518,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,20 +2550,23 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-33600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-30400</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2408,8 +2582,11 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,20 +2678,23 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-5600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2900</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,8 +2710,11 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,71 +2742,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-2000</v>
-      </c>
       <c r="G81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,37 +2827,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,37 +3017,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1900</v>
-      </c>
       <c r="G89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,8 +3065,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2874,8 +3095,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,37 +3159,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,8 +3207,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3003,8 +3237,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,28 +3333,31 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -3119,8 +3365,11 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3148,33 +3397,39 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-1200</v>
-      </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,63 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -743,8 +747,11 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -775,8 +782,11 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,8 +817,11 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,40 +834,44 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,8 +902,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -917,8 +937,11 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -949,8 +972,11 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,40 +986,44 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1001,31 +1031,34 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,8 +1071,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1047,13 +1081,13 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>-200</v>
+        <v>-2900</v>
       </c>
       <c r="F20" s="3">
         <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1061,8 +1095,8 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1070,16 +1104,19 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="E21" s="3">
+        <v>-5300</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
@@ -1102,8 +1139,11 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1113,17 +1153,17 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1134,40 +1174,46 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1198,8 +1244,11 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,72 +1279,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,8 +1489,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1431,13 +1501,13 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>200</v>
+        <v>2900</v>
       </c>
       <c r="F32" s="3">
         <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1445,8 +1515,8 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1454,40 +1524,46 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,77 +1594,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,23 +1701,24 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,8 +1734,11 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1679,8 +1769,11 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1711,8 +1804,11 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1743,23 +1839,26 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,23 +1874,26 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E46" s="3">
         <v>9400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2200</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,8 +1909,11 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1839,8 +1944,11 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1850,8 +1958,8 @@
       <c r="E48" s="3">
         <v>0</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
+      <c r="F48" s="3">
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1871,8 +1979,11 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1903,8 +2014,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,23 +2084,26 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,8 +2119,11 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,23 +2154,26 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E54" s="3">
         <v>9400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2400</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2063,8 +2189,11 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,23 +2221,24 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2254,11 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2155,22 +2289,25 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2187,8 +2324,11 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2196,14 +2336,14 @@
         <v>800</v>
       </c>
       <c r="E60" s="3">
+        <v>800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2219,8 +2359,11 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2228,14 +2371,14 @@
         <v>1000</v>
       </c>
       <c r="E61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F61" s="3">
         <v>1500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2251,23 +2394,26 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4800</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2283,8 +2429,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,8 +2534,11 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2388,14 +2546,14 @@
         <v>1800</v>
       </c>
       <c r="E66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F66" s="3">
         <v>7400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5300</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2411,8 +2569,11 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,23 +2724,26 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-33600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2585,8 +2759,11 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,23 +2864,26 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E76" s="3">
         <v>7600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2900</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2713,8 +2899,11 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,77 +2934,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,16 +3026,17 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -2854,14 +3053,17 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-600</v>
       </c>
       <c r="H89" s="3">
         <v>-600</v>
       </c>
       <c r="I89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,8 +3286,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3098,8 +3319,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,16 +3389,19 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -3188,14 +3418,17 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,8 +3441,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3240,8 +3474,11 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,31 +3579,34 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>9700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3368,8 +3614,11 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3400,36 +3649,42 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>7400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,90 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -750,8 +755,11 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +793,11 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +831,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,43 +849,47 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
-        <v>800</v>
-      </c>
       <c r="H12" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I12" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J12" s="3">
+        <v>400</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,31 +923,34 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -940,8 +961,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +999,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,8 +1014,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -996,69 +1024,75 @@
         <v>2800</v>
       </c>
       <c r="E17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
-        <v>6700</v>
-      </c>
       <c r="H17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>900</v>
+      </c>
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
-        <v>500</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2800</v>
       </c>
       <c r="E18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-6700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,34 +1106,35 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>-2900</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>-200</v>
+        <v>3000</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+        <v>4800</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1107,31 +1142,34 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-2800</v>
       </c>
       <c r="E21" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-2700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1142,8 +1180,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1156,14 +1197,14 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1177,66 +1218,72 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1247,8 +1294,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,34 +1560,37 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>2900</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>200</v>
+        <v>-3000</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+        <v>-4800</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1527,43 +1598,49 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,31 +1789,32 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2100</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1737,8 +1825,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1772,31 +1863,34 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1807,31 +1901,34 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1842,26 +1939,29 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,31 +1977,34 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E46" s="3">
         <v>7100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2200</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="J46" s="3">
+        <v>900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1912,31 +2015,34 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1947,8 +2053,11 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1961,8 +2070,8 @@
       <c r="F48" s="3">
         <v>0</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+      <c r="G48" s="3">
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1982,8 +2091,11 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2129,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,8 +2205,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2098,11 +2219,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>200</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2122,8 +2243,11 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,31 +2281,34 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
         <v>7100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2400</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>900</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2192,8 +2319,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,31 +2353,32 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2257,8 +2389,11 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2292,22 +2427,25 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>500</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2327,31 +2465,34 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="E60" s="3">
         <v>800</v>
       </c>
       <c r="F60" s="3">
+        <v>800</v>
+      </c>
+      <c r="G60" s="3">
         <v>1000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>200</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2362,26 +2503,29 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E61" s="3">
         <v>1000</v>
       </c>
       <c r="F61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2397,8 +2541,11 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2408,15 +2555,15 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>5000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2579,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,31 +2693,34 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="E66" s="3">
         <v>1800</v>
       </c>
       <c r="F66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G66" s="3">
         <v>7400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2572,8 +2731,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,31 +2899,34 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-30400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>-23500</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2762,8 +2937,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,31 +3051,34 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>600</v>
+      </c>
+      <c r="J76" s="3">
+        <v>600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2902,8 +3089,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
-        <v>44926</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
-        <v>-6900</v>
-      </c>
       <c r="H81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,16 +3226,17 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3056,14 +3256,17 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3508,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3304,14 +3526,14 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3322,8 +3544,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,8 +3620,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3403,11 +3634,11 @@
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3421,14 +3652,17 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,31 +3676,32 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3477,8 +3712,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,34 +3826,37 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>9700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
-        <v>3100</v>
-      </c>
       <c r="H100" s="3">
+        <v>400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
@@ -3617,31 +3864,34 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3652,39 +3902,45 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
-        <v>1300</v>
-      </c>
       <c r="H102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>-600</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,72 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -746,8 +749,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -758,8 +761,11 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,8 +802,11 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,8 +843,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,46 +862,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>800</v>
       </c>
-      <c r="G12" s="3">
-        <v>600</v>
-      </c>
       <c r="H12" s="3">
+        <v>700</v>
+      </c>
+      <c r="I12" s="3">
         <v>500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>400</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
+        <v>400</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +942,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -952,8 +971,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -964,8 +983,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1024,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1040,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="E17" s="3">
         <v>2800</v>
       </c>
       <c r="F17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G17" s="3">
         <v>2400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="E18" s="3">
         <v>-2800</v>
       </c>
       <c r="F18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1139,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1118,26 +1151,26 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1145,35 +1178,38 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,8 +1219,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1200,8 +1239,8 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1221,46 +1260,52 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1285,8 +1330,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1297,8 +1342,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1383,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1506,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1547,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1588,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1629,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,26 +1643,26 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1601,46 +1670,52 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1752,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1858,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,35 +1875,36 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E41" s="3">
         <v>5200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,8 +1914,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,8 +1955,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1892,8 +1984,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -1904,8 +1996,11 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1930,8 +2025,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1942,29 +2037,32 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1980,35 +2078,38 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2200</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,8 +2119,11 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2044,8 +2148,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2056,8 +2160,11 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2073,8 +2180,8 @@
       <c r="G48" s="3">
         <v>0</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
+      <c r="H48" s="3">
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
@@ -2094,8 +2201,11 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2132,8 +2242,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2283,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,8 +2324,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2246,8 +2365,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,35 +2406,38 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>900</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2322,8 +2447,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2466,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,35 +2483,36 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,13 +2522,16 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2430,8 +2563,11 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2468,35 +2604,38 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1300</v>
-      </c>
-      <c r="E60" s="3">
-        <v>800</v>
       </c>
       <c r="F60" s="3">
         <v>800</v>
       </c>
       <c r="G60" s="3">
+        <v>800</v>
+      </c>
+      <c r="H60" s="3">
         <v>1000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,29 +2645,32 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1000</v>
       </c>
       <c r="F61" s="3">
         <v>1000</v>
       </c>
       <c r="G61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H61" s="3">
         <v>1500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2544,8 +2686,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2558,15 +2703,15 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>5000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2582,8 +2727,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2768,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2809,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,35 +2850,38 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1800</v>
       </c>
       <c r="F66" s="3">
         <v>1800</v>
       </c>
       <c r="G66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H66" s="3">
         <v>7400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5300</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,8 +2891,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2910,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2949,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2990,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3031,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,35 +3072,38 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-44500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-39000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-33600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-30400</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-23500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3113,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3154,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3195,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,34 +3236,37 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-5600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>600</v>
       </c>
       <c r="J76" s="3">
         <v>600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
+      <c r="K76" s="3">
+        <v>600</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
@@ -3092,8 +3277,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3318,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,13 +3424,14 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -3259,14 +3457,17 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3504,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3545,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3586,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3627,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3668,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,8 +3728,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3526,8 +3746,8 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
@@ -3535,8 +3755,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -3547,8 +3767,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3808,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,8 +3849,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3640,8 +3869,8 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -3655,14 +3884,17 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,8 +3909,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3703,8 +3936,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -3715,8 +3948,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3989,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4030,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,37 +4071,40 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>9000</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>9700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -3867,8 +4112,11 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3893,8 +4141,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3905,42 +4153,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,75 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,11 +760,11 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -764,8 +772,14 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,8 +819,14 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -846,8 +866,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,49 +889,57 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E12" s="3">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="F12" s="3">
         <v>1000</v>
       </c>
       <c r="G12" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="H12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +979,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -974,11 +1014,11 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -986,8 +1026,14 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,8 +1073,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1093,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,8 +1206,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1154,81 +1222,93 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2700</v>
+        <v>-3400</v>
       </c>
       <c r="E21" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F21" s="3">
         <v>-2700</v>
       </c>
       <c r="G21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1242,11 +1322,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1263,49 +1343,61 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E23" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F23" s="3">
         <v>-2700</v>
       </c>
       <c r="G23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-800</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1333,11 +1425,11 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1345,8 +1437,14 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1484,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E26" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F26" s="3">
         <v>-2700</v>
       </c>
       <c r="G26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I26" s="3">
         <v>-5400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E27" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F27" s="3">
         <v>-2700</v>
       </c>
       <c r="G27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1625,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1672,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1719,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,8 +1766,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1646,76 +1786,88 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E33" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F33" s="3">
         <v>-2700</v>
       </c>
       <c r="G33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1907,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E35" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F35" s="3">
         <v>-2700</v>
       </c>
       <c r="G35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +2029,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,49 +2048,57 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1958,8 +2138,14 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1987,11 +2173,11 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -1999,8 +2185,14 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2028,11 +2220,11 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2040,35 +2232,41 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,49 +2279,61 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F46" s="3">
         <v>11900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2200</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2151,11 +2361,11 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2163,8 +2373,14 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2183,11 +2399,11 @@
       <c r="H48" s="3">
         <v>0</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2204,8 +2420,14 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2245,8 +2467,14 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2514,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,8 +2561,14 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2368,8 +2608,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2655,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F54" s="3">
         <v>12000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>7100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3">
         <v>900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2725,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,61 +2744,69 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -2566,8 +2834,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2607,49 +2881,61 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2657,26 +2943,26 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2689,8 +2975,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2706,18 +2998,18 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>5000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>4800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,8 +3022,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +3069,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +3116,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3163,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3233,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3276,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3323,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3370,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3417,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-47200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-44500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-41700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-39000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-33600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-30400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-23500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3511,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3558,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3605,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F76" s="3">
         <v>9700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-5600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-2900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3699,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2700</v>
+        <v>-3300</v>
       </c>
       <c r="E81" s="3">
-        <v>-2800</v>
+        <v>-3200</v>
       </c>
       <c r="F81" s="3">
         <v>-2700</v>
       </c>
       <c r="G81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,19 +3821,21 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -3460,14 +3858,20 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3911,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3958,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +4005,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +4052,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +4099,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-600</v>
       </c>
       <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-700</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,13 +4169,15 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3749,20 +4191,20 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -3770,8 +4212,14 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4259,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,13 +4306,19 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -3872,11 +4332,11 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3887,14 +4347,20 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4376,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3939,11 +4407,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -3951,8 +4419,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4466,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4513,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,49 +4560,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F100" s="3">
         <v>9000</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>9700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>700</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4144,11 +4642,11 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4156,45 +4654,57 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F102" s="3">
         <v>6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,87 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -773,8 +776,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -785,8 +788,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,8 +841,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -885,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,58 +917,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2400</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1600</v>
       </c>
       <c r="F12" s="3">
         <v>1600</v>
       </c>
       <c r="G12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H12" s="3">
         <v>1000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>700</v>
       </c>
       <c r="L12" s="3">
+        <v>700</v>
+      </c>
+      <c r="M12" s="3">
         <v>500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>400</v>
       </c>
       <c r="N12" s="3">
         <v>400</v>
       </c>
       <c r="O12" s="3">
+        <v>400</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1043,8 +1062,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1055,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2800</v>
       </c>
       <c r="I17" s="3">
         <v>2800</v>
       </c>
       <c r="J17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2800</v>
       </c>
       <c r="I18" s="3">
         <v>-2800</v>
       </c>
       <c r="J18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,8 +1274,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1265,26 +1298,26 @@
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1292,47 +1325,50 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1353,8 +1392,8 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1371,8 +1410,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1392,58 +1431,64 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1480,8 +1525,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1492,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,8 +1908,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1865,26 +1934,26 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1892,58 +1961,64 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,47 +2222,48 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E41" s="3">
         <v>7500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,8 +2326,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2275,8 +2367,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2287,8 +2379,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2325,8 +2420,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2337,41 +2432,44 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,47 +2485,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2200</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,8 +2538,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2475,8 +2579,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2487,8 +2591,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2516,8 +2623,8 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+      <c r="L48" s="3">
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2537,8 +2644,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2803,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,47 +2909,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2400</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,47 +3006,48 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E57" s="3">
         <v>800</v>
       </c>
       <c r="F57" s="3">
+        <v>800</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,8 +3057,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2942,11 +3075,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -2977,8 +3110,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3027,47 +3163,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>800</v>
       </c>
       <c r="J60" s="3">
         <v>800</v>
       </c>
       <c r="K60" s="3">
+        <v>800</v>
+      </c>
+      <c r="L60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,8 +3216,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3095,23 +3237,23 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>1100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1000</v>
       </c>
       <c r="J61" s="3">
         <v>1000</v>
       </c>
       <c r="K61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L61" s="3">
         <v>1500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3127,8 +3269,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3153,15 +3298,15 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>5000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3177,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,47 +3481,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1800</v>
       </c>
       <c r="J66" s="3">
         <v>1800</v>
       </c>
       <c r="K66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L66" s="3">
         <v>7400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5300</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,47 +3767,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-61200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-53700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-50400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-47200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-44500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-41700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-39000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-33600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>-23500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,46 +3979,49 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E76" s="3">
         <v>6400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-5600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2900</v>
-      </c>
-      <c r="M76" s="3">
-        <v>600</v>
       </c>
       <c r="N76" s="3">
         <v>600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>600</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -3847,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4039,8 +4237,8 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -4066,14 +4264,17 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,19 +4611,20 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -4421,8 +4641,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -4430,8 +4650,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -4442,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,19 +4768,22 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -4571,8 +4800,8 @@
       <c r="K94" s="3">
         <v>0</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4586,14 +4815,17 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4650,8 +4883,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4662,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,49 +5054,52 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9000</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>9700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>700</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -4862,8 +5107,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4900,8 +5148,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -4912,54 +5160,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMIX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>AMIX</t>
   </si>
@@ -656,90 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -779,8 +783,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -791,8 +795,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +851,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,61 +931,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2400</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1600</v>
       </c>
       <c r="G12" s="3">
         <v>1600</v>
       </c>
       <c r="H12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
       </c>
       <c r="L12" s="3">
         <v>700</v>
       </c>
       <c r="M12" s="3">
+        <v>700</v>
+      </c>
+      <c r="N12" s="3">
         <v>500</v>
-      </c>
-      <c r="N12" s="3">
-        <v>400</v>
       </c>
       <c r="O12" s="3">
         <v>400</v>
       </c>
       <c r="P12" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1041,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1065,8 +1085,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1077,8 +1097,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1174,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2800</v>
       </c>
       <c r="J17" s="3">
         <v>2800</v>
       </c>
       <c r="K17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-2800</v>
       </c>
       <c r="J18" s="3">
         <v>-2800</v>
       </c>
       <c r="K18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1308,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1301,26 +1335,26 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4800</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1328,50 +1362,53 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1395,8 +1435,8 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1413,8 +1453,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1434,61 +1474,67 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1528,8 +1574,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1978,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1937,26 +2007,26 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4800</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1964,61 +2034,67 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,50 +2309,51 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2363,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,8 +2419,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2370,8 +2463,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2382,8 +2475,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2423,8 +2519,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2435,44 +2531,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
       </c>
       <c r="F45" s="3">
         <v>400</v>
       </c>
       <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,50 +2587,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E46" s="3">
         <v>10200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2200</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2643,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2582,8 +2687,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2594,8 +2699,11 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2626,8 +2734,8 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,50 +3035,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E54" s="3">
         <v>10200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2400</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3091,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,8 +3137,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3016,41 +3147,41 @@
         <v>700</v>
       </c>
       <c r="E57" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F57" s="3">
         <v>800</v>
       </c>
       <c r="G57" s="3">
+        <v>800</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,8 +3191,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3078,11 +3212,11 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3113,8 +3247,11 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3166,8 +3303,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3175,41 +3315,41 @@
         <v>1700</v>
       </c>
       <c r="E60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>800</v>
       </c>
       <c r="K60" s="3">
         <v>800</v>
       </c>
       <c r="L60" s="3">
+        <v>800</v>
+      </c>
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3359,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3240,23 +3383,23 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>1000</v>
       </c>
       <c r="L61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3272,8 +3415,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3301,15 +3447,15 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>5000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,8 +3639,11 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3493,41 +3651,41 @@
         <v>1700</v>
       </c>
       <c r="E66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F66" s="3">
         <v>1500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1800</v>
       </c>
       <c r="K66" s="3">
         <v>1800</v>
       </c>
       <c r="L66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M66" s="3">
         <v>7400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3695,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,50 +3941,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-67100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-64400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-61200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-53700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-50400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>-23500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3997,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,49 +4165,52 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E76" s="3">
         <v>8600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-5600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-2900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>600</v>
       </c>
       <c r="O76" s="3">
         <v>600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>600</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -4035,8 +4221,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4418,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4240,8 +4439,8 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -4267,14 +4466,17 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,22 +4832,23 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4644,8 +4865,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4653,8 +4874,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,22 +4998,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -4803,8 +5033,8 @@
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4818,14 +5048,17 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4886,8 +5120,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,52 +5300,55 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>5400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>9700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>700</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5356,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5151,8 +5400,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5163,57 +5412,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
